--- a/manufacturing_forms/006_flow_rate_calculation_form--manufacturing_forms.xlsx
+++ b/manufacturing_forms/006_flow_rate_calculation_form--manufacturing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1215,17 +1215,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>form_flow_rate_units_choices</t>
+          <t>form_flow_rate_validation_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>m2/s</t>
+          <t>valid</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>m2/s</t>
+          <t>Valid</t>
         </is>
       </c>
     </row>
@@ -1237,29 +1237,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>valid</t>
+          <t>invalid</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Valid</t>
+          <t>Invalid</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>form_flow_rate_validation_choices</t>
+          <t>form_flow_rate_calculation_units_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>invalid</t>
+          <t>m3/h</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Invalid</t>
+          <t>m3/h</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>m3/h</t>
+          <t>m3/s</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>m3/h</t>
+          <t>m3/s</t>
         </is>
       </c>
     </row>
@@ -1288,29 +1288,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>m3/s</t>
+          <t>m3/min</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>m3/s</t>
+          <t>m3/min</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>form_flow_rate_calculation_units_choices</t>
+          <t>form_flow_rate_result_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>m3/min</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>m3/min</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1322,29 +1322,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>form_flow_rate_result_choices</t>
+          <t>form_flow_rate_validation_result_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -1356,29 +1356,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>form_flow_rate_validation_result_choices</t>
+          <t>form_flow_rate_calculation_result_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>fail</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1390,29 +1390,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>form_flow_rate_calculation_result_choices</t>
+          <t>form_flow_rate_result_units_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>m3/h</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>m3/h</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>m3/h</t>
+          <t>m3/s</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>m3/h</t>
+          <t>m3/s</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>m3/s</t>
+          <t>m3/min</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>m3/s</t>
+          <t>m3/min</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>m3/min</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>m3/min</t>
+          <t>m3</t>
         </is>
       </c>
     </row>
@@ -1475,53 +1475,53 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2/s</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2/s</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>form_flow_rate_result_units_choices</t>
+          <t>form_flow_rate_result_validation_result_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>m2/s</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>m2/s</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>form_flow_rate_result_units_choices</t>
+          <t>form_flow_rate_result_validation_result_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>m2/s</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>m2/s</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>form_flow_rate_result_validation_result_choices</t>
+          <t>form_flow_rate_calculation_validation_result_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1538,7 +1538,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>form_flow_rate_result_validation_result_choices</t>
+          <t>form_flow_rate_calculation_validation_result_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1555,34 +1555,34 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>form_flow_rate_calculation_validation_result_choices</t>
+          <t>form_flow_rate_calculation_result_units_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>m3/h</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>m3/h</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>form_flow_rate_calculation_validation_result_choices</t>
+          <t>form_flow_rate_calculation_result_units_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>fail</t>
+          <t>m3/s</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>m3/s</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1594,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>m3/h</t>
+          <t>m3/min</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>m3/h</t>
+          <t>m3/min</t>
         </is>
       </c>
     </row>
@@ -1611,12 +1611,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>m3/s</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>m3/s</t>
+          <t>m3</t>
         </is>
       </c>
     </row>
@@ -1628,61 +1628,10 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>m3/min</t>
+          <t>m2/s</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
-        <is>
-          <t>m3/min</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>form_flow_rate_calculation_result_units_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>m3</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>m3</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>form_flow_rate_calculation_result_units_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>m2/s</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>m2/s</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>form_flow_rate_calculation_result_units_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>m2/s</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
         <is>
           <t>m2/s</t>
         </is>
